--- a/report_forms/028_product_spoilage_detection_report_form--report_forms.xlsx
+++ b/report_forms/028_product_spoilage_detection_report_form--report_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -746,8 +746,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="29" customWidth="1" min="2" max="2"/>
-    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -775,12 +775,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'leaking'}</t>
+          <t>leaking</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Leaking'}</t>
+          <t>Leaking</t>
         </is>
       </c>
     </row>
@@ -792,12 +792,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'moldy'}</t>
+          <t>moldy</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Moldy'}</t>
+          <t>Moldy</t>
         </is>
       </c>
     </row>
@@ -809,12 +809,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'rotten'}</t>
+          <t>rotten</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Rotten'}</t>
+          <t>Rotten</t>
         </is>
       </c>
     </row>
@@ -826,12 +826,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'sour'}</t>
+          <t>sour</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Sour'}</t>
+          <t>Sour</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'swollen'}</t>
+          <t>swollen</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Swollen'}</t>
+          <t>Swollen</t>
         </is>
       </c>
     </row>
@@ -860,12 +860,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -877,12 +877,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'new'}</t>
+          <t>new</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'New'}</t>
+          <t>New</t>
         </is>
       </c>
     </row>
@@ -894,12 +894,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'used'}</t>
+          <t>used</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Used'}</t>
+          <t>Used</t>
         </is>
       </c>
     </row>
@@ -911,12 +911,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'damaged'}</t>
+          <t>damaged</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Damaged'}</t>
+          <t>Damaged</t>
         </is>
       </c>
     </row>
@@ -928,12 +928,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'expiration'}</t>
+          <t>expiration</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Expiration'}</t>
+          <t>Expiration</t>
         </is>
       </c>
     </row>
@@ -945,12 +945,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -962,12 +962,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'warehouse'}</t>
+          <t>warehouse</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Warehouse'}</t>
+          <t>Warehouse</t>
         </is>
       </c>
     </row>
@@ -979,12 +979,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'retail'}</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Retail'}</t>
+          <t>Retail</t>
         </is>
       </c>
     </row>
@@ -996,12 +996,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'manufacturing'}</t>
+          <t>manufacturing</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Manufacturing'}</t>
+          <t>Manufacturing</t>
         </is>
       </c>
     </row>
@@ -1013,12 +1013,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'transportation'}</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Transportation'}</t>
+          <t>Transportation</t>
         </is>
       </c>
     </row>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1047,12 +1047,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'replaced'}</t>
+          <t>replaced</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Replaced'}</t>
+          <t>Replaced</t>
         </is>
       </c>
     </row>
@@ -1064,12 +1064,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'reboxed'}</t>
+          <t>reboxed</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Reboxed'}</t>
+          <t>Reboxed</t>
         </is>
       </c>
     </row>
@@ -1081,12 +1081,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'discarded'}</t>
+          <t>discarded</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Discarded'}</t>
+          <t>Discarded</t>
         </is>
       </c>
     </row>
@@ -1098,12 +1098,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
